--- a/exports/treasury/treasury_curveTradesRecap_avgTrades.xlsx
+++ b/exports/treasury/treasury_curveTradesRecap_avgTrades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riccardo/Desktop/Personal Projects/Latest/Yield curve models/gauss+/exports/treasury/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E10735-2E80-9C4F-9D09-2C89F5277B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B961F633-EB19-394E-A199-54FF8C2ACC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="680" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11680" yWindow="960" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="output" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
     <t>Source: BSIC</t>
   </si>
   <si>
-    <t>U.S. Treasuries, number of trades</t>
+    <t>U.S. Treasuries, average trades per item</t>
   </si>
 </sst>
 </file>
@@ -570,7 +570,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
@@ -583,7 +583,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
